--- a/BKQBF_TAB-6.xlsx
+++ b/BKQBF_TAB-6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{E45ECF03-8BBF-43CE-AC78-00B76E360356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01BA480A-8FFC-41D7-8BF6-743181142758}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{E45ECF03-8BBF-43CE-AC78-00B76E360356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC8426AD-DFB6-4BBF-BC22-BF7933DC6C11}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{1AA8A838-AA6C-419E-91A0-2F2725546F0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1AA8A838-AA6C-419E-91A0-2F2725546F0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabela Base Franquias" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6734" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7244" uniqueCount="1357">
   <si>
     <t>Tipologia</t>
   </si>
@@ -3714,17 +3714,416 @@
   </si>
   <si>
     <t>PRECOSP</t>
+  </si>
+  <si>
+    <t>LENCO UMEDECIDO CX1000UN</t>
+  </si>
+  <si>
+    <t>3005.90.90  -20</t>
+  </si>
+  <si>
+    <t>BRINDE COMO TREINAR SEU DRAGAO CX200UN 6MOD</t>
+  </si>
+  <si>
+    <t>LIVRO BOBBIE GOODS CX50UN</t>
+  </si>
+  <si>
+    <t>4901.99.00  -20</t>
+  </si>
+  <si>
+    <t>CASALIVROS</t>
+  </si>
+  <si>
+    <t>COROA BK BOBBIE GOODS CX500UN</t>
+  </si>
+  <si>
+    <t>GRAFICATUD</t>
+  </si>
+  <si>
+    <t>FUNDO BANDEJA BOBBIE GOODS CX1000UN</t>
+  </si>
+  <si>
+    <t>BRINDE SUPERMAN CX100UN MIX 8MOD</t>
+  </si>
+  <si>
+    <t>TOMATE CARMEM ESTADO NATURAL JFC BK</t>
+  </si>
+  <si>
+    <t>ZAMP ITAPE</t>
+  </si>
+  <si>
+    <t>LAMINA WHOPPER BK TRENIER 2025 FD3000UN</t>
+  </si>
+  <si>
+    <t>LAMINA CHICKEN BK 2025 TRENIER FD3000UN</t>
+  </si>
+  <si>
+    <t>LAMINA KING JUNIOR 2025 TRENIER FD3000UN</t>
+  </si>
+  <si>
+    <t>BRINDE NARUTO 8MOD CX200UN</t>
+  </si>
+  <si>
+    <t>LAMINA BIG KING BKC TRENIER FD3000UN</t>
+  </si>
+  <si>
+    <t>LAMINA KING JR 2025 C.CLARO PCT3000UN</t>
+  </si>
+  <si>
+    <t>LAMINA CHICKEN BK 2025 C.CLARO PCT3000UN</t>
+  </si>
+  <si>
+    <t>LAMINA WHOPPER BK C.CLARO 2025 PCT3000UN</t>
+  </si>
+  <si>
+    <t>LAMINA BIG KING BK C.CLARO PCT3000UN</t>
+  </si>
+  <si>
+    <t>PROTEINA SORO DE LEITE CX 12UNX800GR</t>
+  </si>
+  <si>
+    <t>FROZEN CHICKEN NUGGETS BKC CX C/ 8PCT</t>
+  </si>
+  <si>
+    <t>1602.32.3002-20</t>
+  </si>
+  <si>
+    <t>REFRIO 3</t>
+  </si>
+  <si>
+    <t>COPO BK 440ML CX900UN PEPSI 2025</t>
+  </si>
+  <si>
+    <t>BRINDE SONIC CX 6 MODELOS C/200UN</t>
+  </si>
+  <si>
+    <t>COROA SONIC CX C/500UN</t>
+  </si>
+  <si>
+    <t>LAMINA BANDEJA BOB ESPONJA</t>
+  </si>
+  <si>
+    <t>COROA BOB ESPONJA CX C/500UN</t>
+  </si>
+  <si>
+    <t>BRINDE BOB ESPONJA MIX 6 MOD CX 200UND</t>
+  </si>
+  <si>
+    <t>HAMBURGUER VEGT SABOR PICANHA CX122</t>
+  </si>
+  <si>
+    <t>SACO BATATA BOB ESPONJA 2025 CX 1000UN</t>
+  </si>
+  <si>
+    <t>BISCOITO BISCOFF CX C 300UND</t>
+  </si>
+  <si>
+    <t>1905.31.0001-20</t>
+  </si>
+  <si>
+    <t>AURORA</t>
+  </si>
+  <si>
+    <t>CRUMBS BISCOFF CX C 6KG 8X750G</t>
+  </si>
+  <si>
+    <t>SUCO UVA E MACA 300ML FD12</t>
+  </si>
+  <si>
+    <t>NATURAL1</t>
+  </si>
+  <si>
+    <t>SUCO LARANJA MACA 300ML FD12</t>
+  </si>
+  <si>
+    <t>SUCO MARACUJA MACA 300ML FD12</t>
+  </si>
+  <si>
+    <t>COPO POTE BOB ESPONJA 290ML CX 320UN</t>
+  </si>
+  <si>
+    <t>COROA TARTARUGAS NINJAS 2025 CX500UN</t>
+  </si>
+  <si>
+    <t>BRINDE TARTARUGAS NINJAS CX MIX 6 MOD C/200UN</t>
+  </si>
+  <si>
+    <t>9503.00.39  -00</t>
+  </si>
+  <si>
+    <t>ETIQUETA 58X100CM BR SHENZEN</t>
+  </si>
+  <si>
+    <t>4821.90.0001-20</t>
+  </si>
+  <si>
+    <t>ALFACE AMERICANA 48MM</t>
+  </si>
+  <si>
+    <t>0705.11.00  -99</t>
+  </si>
+  <si>
+    <t>JFC NAT</t>
+  </si>
+  <si>
+    <t>TAMPA DOMO BK MIX DLV CX C/2000UN</t>
+  </si>
+  <si>
+    <t>4823.69.00  -99</t>
+  </si>
+  <si>
+    <t>BEBIDA LACTEA BAUNILHA UHT 22,2 KG DIS</t>
+  </si>
+  <si>
+    <t>CAIXA BK THE KINGS C/375UN 2026</t>
+  </si>
+  <si>
+    <t>COROA CARTOON CX C/500UN 2026</t>
+  </si>
+  <si>
+    <t>4819.50.00  -99</t>
+  </si>
+  <si>
+    <t>BRINDE CARTOON NETWORK CLASSICS CX MIX 10 MODELOS C/100UN</t>
+  </si>
+  <si>
+    <t>CARNE FRALDINHA DESF DEFUMADA CX 4KG 4X1</t>
+  </si>
+  <si>
+    <t>BISCOITO AZUL GRANULADO CX C/3KG 3X1</t>
+  </si>
+  <si>
+    <t>QUEIJO PROC CHEDDAR FAT CX 1536UN 2026</t>
+  </si>
+  <si>
+    <t>COCA COLA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>GUARANA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>GUARANA ZERO LATA DLV BK</t>
+  </si>
+  <si>
+    <t>SPRITE LATA DLV BK</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO LATA DLV BK</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA DLV BK</t>
+  </si>
+  <si>
+    <t>COCA COLA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>GUARANA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>GUARANA ZERO LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>SPRITE LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA BALCAO BK</t>
+  </si>
+  <si>
+    <t>REFRIGERANTE GUARANA LATA</t>
+  </si>
+  <si>
+    <t>GUARANA DIET LATA</t>
+  </si>
+  <si>
+    <t>241000000093</t>
+  </si>
+  <si>
+    <t>COCA-COLA LATA 12UN 350ML  DIS</t>
+  </si>
+  <si>
+    <t>241000000094</t>
+  </si>
+  <si>
+    <t>COCA-COLA ZERO LATA 12UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000101</t>
+  </si>
+  <si>
+    <t>COCA-COLA LATA 15UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000102</t>
+  </si>
+  <si>
+    <t>COCA-COLA ZERO LATA 6UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000114</t>
+  </si>
+  <si>
+    <t>COCA-COLA ZERO LATA 6UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000116</t>
+  </si>
+  <si>
+    <t>COCA-COLA LATA 6UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000117</t>
+  </si>
+  <si>
+    <t>COCA-COLA LATA 12UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>7210467</t>
+  </si>
+  <si>
+    <t>7210468</t>
+  </si>
+  <si>
+    <t>7210469</t>
+  </si>
+  <si>
+    <t>7210471</t>
+  </si>
+  <si>
+    <t>7210472</t>
+  </si>
+  <si>
+    <t>7210473</t>
+  </si>
+  <si>
+    <t>7210474</t>
+  </si>
+  <si>
+    <t>7210475</t>
+  </si>
+  <si>
+    <t>7210476</t>
+  </si>
+  <si>
+    <t>7210478</t>
+  </si>
+  <si>
+    <t>7210479</t>
+  </si>
+  <si>
+    <t>7210480</t>
+  </si>
+  <si>
+    <t>9013</t>
+  </si>
+  <si>
+    <t>9014</t>
+  </si>
+  <si>
+    <t>241000000099</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA 12UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000108</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA 6UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000115</t>
+  </si>
+  <si>
+    <t>FANTA LARANJA LATA 6UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000098</t>
+  </si>
+  <si>
+    <t>SPRITE LATA 6UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000107</t>
+  </si>
+  <si>
+    <t>SPRITE LATA 6UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000095</t>
+  </si>
+  <si>
+    <t>FANTA GUARANA LATA 6UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000096</t>
+  </si>
+  <si>
+    <t>FANTA GUARANA ZERO LATA 6UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000100</t>
+  </si>
+  <si>
+    <t>KUAT ZERO LATA 6UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000103</t>
+  </si>
+  <si>
+    <t>FANTA GUARANA LATA 6UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000105</t>
+  </si>
+  <si>
+    <t>FANTA GUARANA ZERO LATA 6UN 310ML  DIS</t>
+  </si>
+  <si>
+    <t>241000000109</t>
+  </si>
+  <si>
+    <t>KUAT LATA 6UN 350ML</t>
+  </si>
+  <si>
+    <t>241000000110</t>
+  </si>
+  <si>
+    <t>TUCHAUA LATA 12UN 350ML DIS</t>
+  </si>
+  <si>
+    <t>241000000111</t>
+  </si>
+  <si>
+    <t>KUAT LATA 6UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000112</t>
+  </si>
+  <si>
+    <t>KUAT ZERO LATA 6UN 310ML DIS</t>
+  </si>
+  <si>
+    <t>241000000113</t>
+  </si>
+  <si>
+    <t>TUCHAUA LATA 12UN 310ML  DIS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3765,8 +4164,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3785,8 +4204,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -3837,14 +4274,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF002060"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3897,12 +4374,91 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="29">
+    <cellStyle name="Moeda 2" xfId="6" xr:uid="{E8314131-D7B4-4076-8CC3-1641AC27195D}"/>
+    <cellStyle name="Moeda 2 2" xfId="11" xr:uid="{A7D51765-24D0-43CA-9F04-286B7A5080A4}"/>
+    <cellStyle name="Moeda 2 3" xfId="17" xr:uid="{2B7EFE53-9124-4CC9-BB5C-2A04E6ACBE68}"/>
+    <cellStyle name="Moeda 2 4" xfId="23" xr:uid="{1B5C0E87-A463-4837-9E6C-37DD731668A6}"/>
+    <cellStyle name="Moeda 3" xfId="20" xr:uid="{5A0572A9-D94C-429D-8EDC-5CACFCE18292}"/>
+    <cellStyle name="Moeda 4" xfId="26" xr:uid="{CBEC55AB-80B2-4C1D-9A9A-3BB53E45E19F}"/>
+    <cellStyle name="Moeda 5" xfId="14" xr:uid="{6AC55146-AB18-4809-8083-9BFC4665ACDE}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 16" xfId="8" xr:uid="{1C71200D-6141-4F71-B28B-44E5156B00EF}"/>
+    <cellStyle name="Normal 17" xfId="12" xr:uid="{5FDF6E04-1DDD-480E-87C5-553804592CC7}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{92FBD9B1-4FA5-4EBF-A966-826CF76EF537}"/>
+    <cellStyle name="Normal 3" xfId="27" xr:uid="{8FB8D820-D409-4C4D-9FE4-A1139BA8D366}"/>
+    <cellStyle name="Porcentagem 2" xfId="10" xr:uid="{D4C83861-3874-467D-8AE6-BE756B9E1003}"/>
+    <cellStyle name="Porcentagem 3" xfId="13" xr:uid="{9E27B31B-3F9F-4956-81E9-831E8E214869}"/>
     <cellStyle name="Vírgula 2" xfId="2" xr:uid="{56121163-DAE9-425B-BCAF-228A3A040AE2}"/>
     <cellStyle name="Vírgula 2 2" xfId="3" xr:uid="{89D378EB-023A-4EE5-8F55-0EAFE6E6D19A}"/>
+    <cellStyle name="Vírgula 2 2 2" xfId="16" xr:uid="{FDD8F537-8C12-4BB3-9F04-4F43B3209C39}"/>
+    <cellStyle name="Vírgula 2 2 3" xfId="22" xr:uid="{48144E9F-CACF-4FB4-8942-000842D83872}"/>
+    <cellStyle name="Vírgula 2 2 4" xfId="28" xr:uid="{A56686D6-CEE3-4B66-96EB-079C82E9DC22}"/>
+    <cellStyle name="Vírgula 2 2 5" xfId="5" xr:uid="{5C48AC85-CDA8-4072-AA93-C98DACF51325}"/>
+    <cellStyle name="Vírgula 2 3" xfId="9" xr:uid="{222A16D1-3D9A-4D50-B552-6A216F822765}"/>
+    <cellStyle name="Vírgula 2 3 2" xfId="19" xr:uid="{CB2CFC3B-D0CC-4E3E-97F0-33D5F8BC9C0A}"/>
+    <cellStyle name="Vírgula 2 3 3" xfId="25" xr:uid="{3006D64D-59C6-44A8-BB9F-44BDFAD63F2C}"/>
+    <cellStyle name="Vírgula 3" xfId="4" xr:uid="{EC5ECA13-E0A0-463F-9593-9469CD7D1E2B}"/>
+    <cellStyle name="Vírgula 3 2" xfId="15" xr:uid="{138E838E-1EF8-47DE-9280-7A6EFE37A582}"/>
+    <cellStyle name="Vírgula 3 3" xfId="21" xr:uid="{1AECC9D3-3B4E-4006-B9C0-1B4C4944EC59}"/>
+    <cellStyle name="Vírgula 4" xfId="18" xr:uid="{2075C977-EC38-495F-92CE-E53ABFF44A5B}"/>
+    <cellStyle name="Vírgula 5" xfId="24" xr:uid="{E14F2E3C-2BB3-4A0A-A183-D2B1A4D1911A}"/>
+    <cellStyle name="Vírgula 6" xfId="7" xr:uid="{792BDF78-F625-4EA8-82BA-2DE89C0D1EC3}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3915,6 +4471,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4237,7 +4797,7 @@
   <sheetPr>
     <outlinePr summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AC746"/>
+  <dimension ref="A1:AD826"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="16" customWidth="1"/>
@@ -69750,7 +70310,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="737" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="5" t="s">
         <v>165</v>
       </c>
@@ -69839,7 +70399,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="738" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="5" t="s">
         <v>165</v>
       </c>
@@ -69928,7 +70488,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="739" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="5" t="s">
         <v>165</v>
       </c>
@@ -70017,7 +70577,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="740" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="5" t="s">
         <v>26</v>
       </c>
@@ -70106,7 +70666,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="741" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="5" t="s">
         <v>78</v>
       </c>
@@ -70195,7 +70755,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="742" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="5" t="s">
         <v>26</v>
       </c>
@@ -70284,7 +70844,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="743" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="5" t="s">
         <v>165</v>
       </c>
@@ -70373,7 +70933,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="744" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="5" t="s">
         <v>26</v>
       </c>
@@ -70462,7 +71022,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="745" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="5" t="s">
         <v>26</v>
       </c>
@@ -70551,7 +71111,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="746" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="5" t="s">
         <v>26</v>
       </c>
@@ -70640,38 +71200,3084 @@
         <v>1200</v>
       </c>
     </row>
+    <row r="747" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A747" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B747" s="21">
+        <v>201011600042</v>
+      </c>
+      <c r="C747" s="24">
+        <v>39678</v>
+      </c>
+      <c r="D747" s="20" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E747" s="22" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F747" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G747" s="23">
+        <v>3.16</v>
+      </c>
+      <c r="H747" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="I747" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J747" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K747" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L747" s="35"/>
+      <c r="M747" s="35"/>
+      <c r="N747" s="35"/>
+      <c r="O747" s="35"/>
+      <c r="P747" s="35"/>
+      <c r="Q747" s="35"/>
+      <c r="R747" s="36"/>
+      <c r="S747" s="34"/>
+      <c r="T747" s="37">
+        <v>258.504132815427</v>
+      </c>
+      <c r="U747" s="34"/>
+      <c r="V747" s="34"/>
+      <c r="W747" s="34"/>
+      <c r="X747" s="34"/>
+      <c r="Y747" s="34"/>
+      <c r="Z747" s="34"/>
+      <c r="AA747" s="34"/>
+      <c r="AB747" s="12"/>
+      <c r="AC747" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD747" s="12"/>
+    </row>
+    <row r="748" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A748" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B748" s="26">
+        <v>241000000031</v>
+      </c>
+      <c r="C748" s="28">
+        <v>40104</v>
+      </c>
+      <c r="D748" s="30" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E748" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="F748" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="32">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H748" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="I748" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J748" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K748" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L748" s="35"/>
+      <c r="M748" s="35"/>
+      <c r="N748" s="35"/>
+      <c r="O748" s="35"/>
+      <c r="P748" s="35"/>
+      <c r="Q748" s="35"/>
+      <c r="R748" s="36"/>
+      <c r="S748" s="34"/>
+      <c r="T748" s="37">
+        <v>2206.7225469663376</v>
+      </c>
+      <c r="U748" s="34"/>
+      <c r="V748" s="34"/>
+      <c r="W748" s="34"/>
+      <c r="X748" s="34"/>
+      <c r="Y748" s="34"/>
+      <c r="Z748" s="34"/>
+      <c r="AA748" s="34"/>
+      <c r="AB748" s="12"/>
+      <c r="AC748" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD748" s="12"/>
+    </row>
+    <row r="749" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A749" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B749" s="26">
+        <v>241000000023</v>
+      </c>
+      <c r="C749" s="28">
+        <v>40201</v>
+      </c>
+      <c r="D749" s="30" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E749" s="31" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F749" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G749" s="32">
+        <v>10.3</v>
+      </c>
+      <c r="H749" s="30" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I749" s="33" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J749" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K749" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L749" s="35"/>
+      <c r="M749" s="35"/>
+      <c r="N749" s="35"/>
+      <c r="O749" s="35"/>
+      <c r="P749" s="35"/>
+      <c r="Q749" s="35"/>
+      <c r="R749" s="36"/>
+      <c r="S749" s="34"/>
+      <c r="T749" s="37">
+        <v>469.93604692500003</v>
+      </c>
+      <c r="U749" s="34"/>
+      <c r="V749" s="34"/>
+      <c r="W749" s="34"/>
+      <c r="X749" s="34"/>
+      <c r="Y749" s="34"/>
+      <c r="Z749" s="34"/>
+      <c r="AA749" s="34"/>
+      <c r="AB749" s="12"/>
+      <c r="AC749" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD749" s="12"/>
+    </row>
+    <row r="750" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A750" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B750" s="26">
+        <v>221000000598</v>
+      </c>
+      <c r="C750" s="28">
+        <v>40217</v>
+      </c>
+      <c r="D750" s="30" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E750" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="F750" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G750" s="32">
+        <v>6.44</v>
+      </c>
+      <c r="H750" s="30" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I750" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J750" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K750" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L750" s="35"/>
+      <c r="M750" s="35"/>
+      <c r="N750" s="35"/>
+      <c r="O750" s="35"/>
+      <c r="P750" s="35"/>
+      <c r="Q750" s="35"/>
+      <c r="R750" s="36"/>
+      <c r="S750" s="34"/>
+      <c r="T750" s="37">
+        <v>183.34837195457905</v>
+      </c>
+      <c r="U750" s="34"/>
+      <c r="V750" s="34"/>
+      <c r="W750" s="34"/>
+      <c r="X750" s="34"/>
+      <c r="Y750" s="34"/>
+      <c r="Z750" s="34"/>
+      <c r="AA750" s="34"/>
+      <c r="AB750" s="12"/>
+      <c r="AC750" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD750" s="12"/>
+    </row>
+    <row r="751" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A751" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B751" s="26">
+        <v>221000000597</v>
+      </c>
+      <c r="C751" s="28">
+        <v>40218</v>
+      </c>
+      <c r="D751" s="30" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E751" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="F751" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G751" s="32">
+        <v>4.32</v>
+      </c>
+      <c r="H751" s="30" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I751" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J751" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K751" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L751" s="35"/>
+      <c r="M751" s="35"/>
+      <c r="N751" s="35"/>
+      <c r="O751" s="35"/>
+      <c r="P751" s="35"/>
+      <c r="Q751" s="35"/>
+      <c r="R751" s="36"/>
+      <c r="S751" s="34"/>
+      <c r="T751" s="37">
+        <v>118.60015013102198</v>
+      </c>
+      <c r="U751" s="34"/>
+      <c r="V751" s="34"/>
+      <c r="W751" s="34"/>
+      <c r="X751" s="34"/>
+      <c r="Y751" s="34"/>
+      <c r="Z751" s="34"/>
+      <c r="AA751" s="34"/>
+      <c r="AB751" s="12"/>
+      <c r="AC751" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD751" s="12"/>
+    </row>
+    <row r="752" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A752" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B752" s="26">
+        <v>241000000032</v>
+      </c>
+      <c r="C752" s="28">
+        <v>40286</v>
+      </c>
+      <c r="D752" s="30" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E752" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="F752" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G752" s="32">
+        <v>7.4</v>
+      </c>
+      <c r="H752" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="I752" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J752" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K752" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L752" s="35"/>
+      <c r="M752" s="35"/>
+      <c r="N752" s="35"/>
+      <c r="O752" s="35"/>
+      <c r="P752" s="35"/>
+      <c r="Q752" s="35"/>
+      <c r="R752" s="36"/>
+      <c r="S752" s="34"/>
+      <c r="T752" s="37">
+        <v>1268.9659600215011</v>
+      </c>
+      <c r="U752" s="34"/>
+      <c r="V752" s="34"/>
+      <c r="W752" s="34"/>
+      <c r="X752" s="34"/>
+      <c r="Y752" s="34"/>
+      <c r="Z752" s="34"/>
+      <c r="AA752" s="34"/>
+      <c r="AB752" s="12"/>
+      <c r="AC752" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD752" s="12"/>
+    </row>
+    <row r="753" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A753" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="B753" s="26">
+        <v>201010000342</v>
+      </c>
+      <c r="C753" s="28">
+        <v>40296</v>
+      </c>
+      <c r="D753" s="30" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E753" s="31" t="s">
+        <v>791</v>
+      </c>
+      <c r="F753" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G753" s="32">
+        <v>7.37</v>
+      </c>
+      <c r="H753" s="30" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I753" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J753" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K753" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L753" s="35"/>
+      <c r="M753" s="35"/>
+      <c r="N753" s="35"/>
+      <c r="O753" s="35"/>
+      <c r="P753" s="35"/>
+      <c r="Q753" s="35"/>
+      <c r="R753" s="36"/>
+      <c r="S753" s="34"/>
+      <c r="T753" s="37">
+        <v>97.109579207500005</v>
+      </c>
+      <c r="U753" s="34"/>
+      <c r="V753" s="34"/>
+      <c r="W753" s="34"/>
+      <c r="X753" s="34"/>
+      <c r="Y753" s="34"/>
+      <c r="Z753" s="34"/>
+      <c r="AA753" s="34"/>
+      <c r="AB753" s="12"/>
+      <c r="AC753" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD753" s="12"/>
+    </row>
+    <row r="754" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A754" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B754" s="26">
+        <v>221000000612</v>
+      </c>
+      <c r="C754" s="28">
+        <v>40309</v>
+      </c>
+      <c r="D754" s="30" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E754" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F754" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G754" s="32">
+        <v>10.455</v>
+      </c>
+      <c r="H754" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="I754" s="33" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J754" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K754" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L754" s="35"/>
+      <c r="M754" s="35"/>
+      <c r="N754" s="35"/>
+      <c r="O754" s="35"/>
+      <c r="P754" s="35"/>
+      <c r="Q754" s="35"/>
+      <c r="R754" s="36"/>
+      <c r="S754" s="34"/>
+      <c r="T754" s="37">
+        <v>272.46223202479342</v>
+      </c>
+      <c r="U754" s="34"/>
+      <c r="V754" s="34"/>
+      <c r="W754" s="34"/>
+      <c r="X754" s="34"/>
+      <c r="Y754" s="34"/>
+      <c r="Z754" s="34"/>
+      <c r="AA754" s="34"/>
+      <c r="AB754" s="12"/>
+      <c r="AC754" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD754" s="12"/>
+    </row>
+    <row r="755" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A755" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B755" s="26">
+        <v>221000000615</v>
+      </c>
+      <c r="C755" s="28">
+        <v>40310</v>
+      </c>
+      <c r="D755" s="30" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E755" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F755" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G755" s="32">
+        <v>8.2469999999999999</v>
+      </c>
+      <c r="H755" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="I755" s="33" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J755" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K755" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L755" s="35"/>
+      <c r="M755" s="35"/>
+      <c r="N755" s="35"/>
+      <c r="O755" s="35"/>
+      <c r="P755" s="35"/>
+      <c r="Q755" s="35"/>
+      <c r="R755" s="36"/>
+      <c r="S755" s="34"/>
+      <c r="T755" s="37">
+        <v>211.68257769703686</v>
+      </c>
+      <c r="U755" s="34"/>
+      <c r="V755" s="34"/>
+      <c r="W755" s="34"/>
+      <c r="X755" s="34"/>
+      <c r="Y755" s="34"/>
+      <c r="Z755" s="34"/>
+      <c r="AA755" s="34"/>
+      <c r="AB755" s="12"/>
+      <c r="AC755" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD755" s="12"/>
+    </row>
+    <row r="756" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A756" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B756" s="26">
+        <v>221000000617</v>
+      </c>
+      <c r="C756" s="28">
+        <v>40323</v>
+      </c>
+      <c r="D756" s="30" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E756" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F756" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G756" s="32">
+        <v>8.2469999999999999</v>
+      </c>
+      <c r="H756" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="I756" s="33" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J756" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K756" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L756" s="35"/>
+      <c r="M756" s="35"/>
+      <c r="N756" s="35"/>
+      <c r="O756" s="35"/>
+      <c r="P756" s="35"/>
+      <c r="Q756" s="35"/>
+      <c r="R756" s="36"/>
+      <c r="S756" s="34"/>
+      <c r="T756" s="37">
+        <v>211.68257769703686</v>
+      </c>
+      <c r="U756" s="34"/>
+      <c r="V756" s="34"/>
+      <c r="W756" s="34"/>
+      <c r="X756" s="34"/>
+      <c r="Y756" s="34"/>
+      <c r="Z756" s="34"/>
+      <c r="AA756" s="34"/>
+      <c r="AB756" s="12"/>
+      <c r="AC756" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD756" s="12"/>
+    </row>
+    <row r="757" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A757" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B757" s="26">
+        <v>241000000033</v>
+      </c>
+      <c r="C757" s="28">
+        <v>40338</v>
+      </c>
+      <c r="D757" s="30" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E757" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="F757" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G757" s="32">
+        <v>7.38</v>
+      </c>
+      <c r="H757" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="I757" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J757" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K757" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L757" s="35"/>
+      <c r="M757" s="35"/>
+      <c r="N757" s="35"/>
+      <c r="O757" s="35"/>
+      <c r="P757" s="35"/>
+      <c r="Q757" s="35"/>
+      <c r="R757" s="36"/>
+      <c r="S757" s="34"/>
+      <c r="T757" s="37">
+        <v>2455.6329044614658</v>
+      </c>
+      <c r="U757" s="34"/>
+      <c r="V757" s="34"/>
+      <c r="W757" s="34"/>
+      <c r="X757" s="34"/>
+      <c r="Y757" s="34"/>
+      <c r="Z757" s="34"/>
+      <c r="AA757" s="34"/>
+      <c r="AB757" s="12"/>
+      <c r="AC757" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD757" s="12"/>
+    </row>
+    <row r="758" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A758" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B758" s="26">
+        <v>201030000379</v>
+      </c>
+      <c r="C758" s="28">
+        <v>40362</v>
+      </c>
+      <c r="D758" s="30" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E758" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F758" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G758" s="32">
+        <v>8.2469999999999999</v>
+      </c>
+      <c r="H758" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="I758" s="33" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J758" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K758" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L758" s="35"/>
+      <c r="M758" s="35"/>
+      <c r="N758" s="35"/>
+      <c r="O758" s="35"/>
+      <c r="P758" s="35"/>
+      <c r="Q758" s="35"/>
+      <c r="R758" s="36"/>
+      <c r="S758" s="34"/>
+      <c r="T758" s="37">
+        <v>211.68257769703686</v>
+      </c>
+      <c r="U758" s="34"/>
+      <c r="V758" s="34"/>
+      <c r="W758" s="34"/>
+      <c r="X758" s="34"/>
+      <c r="Y758" s="34"/>
+      <c r="Z758" s="34"/>
+      <c r="AA758" s="34"/>
+      <c r="AB758" s="12"/>
+      <c r="AC758" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD758" s="12"/>
+    </row>
+    <row r="759" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A759" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B759" s="26">
+        <v>221000000617</v>
+      </c>
+      <c r="C759" s="28">
+        <v>40364</v>
+      </c>
+      <c r="D759" s="30" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E759" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F759" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G759" s="32">
+        <v>9.09</v>
+      </c>
+      <c r="H759" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="I759" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J759" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K759" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L759" s="35"/>
+      <c r="M759" s="35"/>
+      <c r="N759" s="35"/>
+      <c r="O759" s="35"/>
+      <c r="P759" s="35"/>
+      <c r="Q759" s="35"/>
+      <c r="R759" s="36"/>
+      <c r="S759" s="34"/>
+      <c r="T759" s="37">
+        <v>192.04300554659682</v>
+      </c>
+      <c r="U759" s="34"/>
+      <c r="V759" s="34"/>
+      <c r="W759" s="34"/>
+      <c r="X759" s="34"/>
+      <c r="Y759" s="34"/>
+      <c r="Z759" s="34"/>
+      <c r="AA759" s="34"/>
+      <c r="AB759" s="12"/>
+      <c r="AC759" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD759" s="12"/>
+    </row>
+    <row r="760" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A760" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B760" s="26">
+        <v>221000000615</v>
+      </c>
+      <c r="C760" s="28">
+        <v>40365</v>
+      </c>
+      <c r="D760" s="30" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E760" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F760" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G760" s="32">
+        <v>9.09</v>
+      </c>
+      <c r="H760" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="I760" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J760" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K760" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L760" s="35"/>
+      <c r="M760" s="35"/>
+      <c r="N760" s="35"/>
+      <c r="O760" s="35"/>
+      <c r="P760" s="35"/>
+      <c r="Q760" s="35"/>
+      <c r="R760" s="36"/>
+      <c r="S760" s="34"/>
+      <c r="T760" s="37">
+        <v>192.04300554659682</v>
+      </c>
+      <c r="U760" s="34"/>
+      <c r="V760" s="34"/>
+      <c r="W760" s="34"/>
+      <c r="X760" s="34"/>
+      <c r="Y760" s="34"/>
+      <c r="Z760" s="34"/>
+      <c r="AA760" s="34"/>
+      <c r="AB760" s="12"/>
+      <c r="AC760" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD760" s="12"/>
+    </row>
+    <row r="761" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A761" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B761" s="26">
+        <v>221000000612</v>
+      </c>
+      <c r="C761" s="28">
+        <v>40366</v>
+      </c>
+      <c r="D761" s="30" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E761" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F761" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G761" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="H761" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="I761" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J761" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K761" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L761" s="35"/>
+      <c r="M761" s="35"/>
+      <c r="N761" s="35"/>
+      <c r="O761" s="35"/>
+      <c r="P761" s="35"/>
+      <c r="Q761" s="35"/>
+      <c r="R761" s="36"/>
+      <c r="S761" s="34"/>
+      <c r="T761" s="37">
+        <v>243.66312279110394</v>
+      </c>
+      <c r="U761" s="34"/>
+      <c r="V761" s="34"/>
+      <c r="W761" s="34"/>
+      <c r="X761" s="34"/>
+      <c r="Y761" s="34"/>
+      <c r="Z761" s="34"/>
+      <c r="AA761" s="34"/>
+      <c r="AB761" s="12"/>
+      <c r="AC761" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD761" s="12"/>
+    </row>
+    <row r="762" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A762" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B762" s="26">
+        <v>201030000379</v>
+      </c>
+      <c r="C762" s="28">
+        <v>40367</v>
+      </c>
+      <c r="D762" s="30" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E762" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="F762" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G762" s="32">
+        <v>9.09</v>
+      </c>
+      <c r="H762" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="I762" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J762" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K762" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L762" s="35"/>
+      <c r="M762" s="35"/>
+      <c r="N762" s="35"/>
+      <c r="O762" s="35"/>
+      <c r="P762" s="35"/>
+      <c r="Q762" s="35"/>
+      <c r="R762" s="36"/>
+      <c r="S762" s="34"/>
+      <c r="T762" s="37">
+        <v>192.04300554659682</v>
+      </c>
+      <c r="U762" s="34"/>
+      <c r="V762" s="34"/>
+      <c r="W762" s="34"/>
+      <c r="X762" s="34"/>
+      <c r="Y762" s="34"/>
+      <c r="Z762" s="34"/>
+      <c r="AA762" s="34"/>
+      <c r="AB762" s="12"/>
+      <c r="AC762" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD762" s="12"/>
+    </row>
+    <row r="763" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A763" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B763" s="26">
+        <v>221000000639</v>
+      </c>
+      <c r="C763" s="28">
+        <v>40442</v>
+      </c>
+      <c r="D763" s="30" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E763" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="F763" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G763" s="32">
+        <v>10.61</v>
+      </c>
+      <c r="H763" s="30" t="s">
+        <v>651</v>
+      </c>
+      <c r="I763" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J763" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K763" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L763" s="35"/>
+      <c r="M763" s="35"/>
+      <c r="N763" s="35"/>
+      <c r="O763" s="35"/>
+      <c r="P763" s="35"/>
+      <c r="Q763" s="35"/>
+      <c r="R763" s="36"/>
+      <c r="S763" s="34"/>
+      <c r="T763" s="37">
+        <v>1289.1883262749443</v>
+      </c>
+      <c r="U763" s="34"/>
+      <c r="V763" s="34"/>
+      <c r="W763" s="34"/>
+      <c r="X763" s="34"/>
+      <c r="Y763" s="34"/>
+      <c r="Z763" s="34"/>
+      <c r="AA763" s="34"/>
+      <c r="AB763" s="12"/>
+      <c r="AC763" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD763" s="12"/>
+    </row>
+    <row r="764" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A764" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B764" s="26">
+        <v>221000000711</v>
+      </c>
+      <c r="C764" s="28">
+        <v>40517</v>
+      </c>
+      <c r="D764" s="30" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E764" s="31" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F764" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G764" s="32">
+        <v>15.47</v>
+      </c>
+      <c r="H764" s="30" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I764" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J764" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K764" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L764" s="35"/>
+      <c r="M764" s="35"/>
+      <c r="N764" s="35"/>
+      <c r="O764" s="35"/>
+      <c r="P764" s="35"/>
+      <c r="Q764" s="35"/>
+      <c r="R764" s="36"/>
+      <c r="S764" s="34"/>
+      <c r="T764" s="37">
+        <v>591.48627787744397</v>
+      </c>
+      <c r="U764" s="34"/>
+      <c r="V764" s="34"/>
+      <c r="W764" s="34"/>
+      <c r="X764" s="34"/>
+      <c r="Y764" s="34"/>
+      <c r="Z764" s="34"/>
+      <c r="AA764" s="34"/>
+      <c r="AB764" s="12"/>
+      <c r="AC764" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD764" s="12"/>
+    </row>
+    <row r="765" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A765" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B765" s="26">
+        <v>221000000664</v>
+      </c>
+      <c r="C765" s="28">
+        <v>40524</v>
+      </c>
+      <c r="D765" s="30" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E765" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="F765" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G765" s="32">
+        <v>8.9</v>
+      </c>
+      <c r="H765" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="I765" s="33" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J765" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K765" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L765" s="35"/>
+      <c r="M765" s="35"/>
+      <c r="N765" s="35"/>
+      <c r="O765" s="35"/>
+      <c r="P765" s="35"/>
+      <c r="Q765" s="35"/>
+      <c r="R765" s="36"/>
+      <c r="S765" s="34"/>
+      <c r="T765" s="37">
+        <v>261.77036387153129</v>
+      </c>
+      <c r="U765" s="34"/>
+      <c r="V765" s="34"/>
+      <c r="W765" s="34"/>
+      <c r="X765" s="34"/>
+      <c r="Y765" s="34"/>
+      <c r="Z765" s="34"/>
+      <c r="AA765" s="34"/>
+      <c r="AB765" s="12"/>
+      <c r="AC765" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD765" s="12"/>
+    </row>
+    <row r="766" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A766" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B766" s="26">
+        <v>241000000035</v>
+      </c>
+      <c r="C766" s="28">
+        <v>40606</v>
+      </c>
+      <c r="D766" s="30" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E766" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="F766" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G766" s="32">
+        <v>6.5</v>
+      </c>
+      <c r="H766" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="I766" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J766" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K766" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L766" s="35"/>
+      <c r="M766" s="35"/>
+      <c r="N766" s="35"/>
+      <c r="O766" s="35"/>
+      <c r="P766" s="35"/>
+      <c r="Q766" s="35"/>
+      <c r="R766" s="36"/>
+      <c r="S766" s="34"/>
+      <c r="T766" s="37">
+        <v>1696.9319974131561</v>
+      </c>
+      <c r="U766" s="34"/>
+      <c r="V766" s="34"/>
+      <c r="W766" s="34"/>
+      <c r="X766" s="34"/>
+      <c r="Y766" s="34"/>
+      <c r="Z766" s="34"/>
+      <c r="AA766" s="34"/>
+      <c r="AB766" s="12"/>
+      <c r="AC766" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD766" s="12"/>
+    </row>
+    <row r="767" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A767" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B767" s="26">
+        <v>221000000677</v>
+      </c>
+      <c r="C767" s="28">
+        <v>40629</v>
+      </c>
+      <c r="D767" s="30" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E767" s="31" t="s">
+        <v>575</v>
+      </c>
+      <c r="F767" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G767" s="32">
+        <v>6.05</v>
+      </c>
+      <c r="H767" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="I767" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J767" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K767" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L767" s="35"/>
+      <c r="M767" s="35"/>
+      <c r="N767" s="35"/>
+      <c r="O767" s="35"/>
+      <c r="P767" s="35"/>
+      <c r="Q767" s="35"/>
+      <c r="R767" s="36"/>
+      <c r="S767" s="34"/>
+      <c r="T767" s="37">
+        <v>135.83615096082781</v>
+      </c>
+      <c r="U767" s="34"/>
+      <c r="V767" s="34"/>
+      <c r="W767" s="34"/>
+      <c r="X767" s="34"/>
+      <c r="Y767" s="34"/>
+      <c r="Z767" s="34"/>
+      <c r="AA767" s="34"/>
+      <c r="AB767" s="12"/>
+      <c r="AC767" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD767" s="12"/>
+    </row>
+    <row r="768" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A768" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B768" s="26">
+        <v>221000000710</v>
+      </c>
+      <c r="C768" s="28">
+        <v>41365</v>
+      </c>
+      <c r="D768" s="30" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E768" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="F768" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G768" s="32">
+        <v>1.875</v>
+      </c>
+      <c r="H768" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="I768" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J768" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K768" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L768" s="35"/>
+      <c r="M768" s="35"/>
+      <c r="N768" s="35"/>
+      <c r="O768" s="35"/>
+      <c r="P768" s="35"/>
+      <c r="Q768" s="35"/>
+      <c r="R768" s="36"/>
+      <c r="S768" s="34"/>
+      <c r="T768" s="37">
+        <v>41.268556616609551</v>
+      </c>
+      <c r="U768" s="34"/>
+      <c r="V768" s="34"/>
+      <c r="W768" s="34"/>
+      <c r="X768" s="34"/>
+      <c r="Y768" s="34"/>
+      <c r="Z768" s="34"/>
+      <c r="AA768" s="34"/>
+      <c r="AB768" s="12"/>
+      <c r="AC768" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD768" s="12"/>
+    </row>
+    <row r="769" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A769" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B769" s="26">
+        <v>221000000717</v>
+      </c>
+      <c r="C769" s="28">
+        <v>41372</v>
+      </c>
+      <c r="D769" s="30" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E769" s="31" t="s">
+        <v>575</v>
+      </c>
+      <c r="F769" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G769" s="32">
+        <v>6.05</v>
+      </c>
+      <c r="H769" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="I769" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J769" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K769" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L769" s="35"/>
+      <c r="M769" s="35"/>
+      <c r="N769" s="35"/>
+      <c r="O769" s="35"/>
+      <c r="P769" s="35"/>
+      <c r="Q769" s="35"/>
+      <c r="R769" s="36"/>
+      <c r="S769" s="34"/>
+      <c r="T769" s="37">
+        <v>135.83615096082781</v>
+      </c>
+      <c r="U769" s="34"/>
+      <c r="V769" s="34"/>
+      <c r="W769" s="34"/>
+      <c r="X769" s="34"/>
+      <c r="Y769" s="34"/>
+      <c r="Z769" s="34"/>
+      <c r="AA769" s="34"/>
+      <c r="AB769" s="12"/>
+      <c r="AC769" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD769" s="12"/>
+    </row>
+    <row r="770" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A770" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B770" s="26">
+        <v>241000000037</v>
+      </c>
+      <c r="C770" s="28">
+        <v>41402</v>
+      </c>
+      <c r="D770" s="30" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E770" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="F770" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G770" s="32">
+        <v>9.5</v>
+      </c>
+      <c r="H770" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="I770" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J770" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K770" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L770" s="35"/>
+      <c r="M770" s="35"/>
+      <c r="N770" s="35"/>
+      <c r="O770" s="35"/>
+      <c r="P770" s="35"/>
+      <c r="Q770" s="35"/>
+      <c r="R770" s="36"/>
+      <c r="S770" s="34"/>
+      <c r="T770" s="37">
+        <v>2518.5302897601287</v>
+      </c>
+      <c r="U770" s="34"/>
+      <c r="V770" s="34"/>
+      <c r="W770" s="34"/>
+      <c r="X770" s="34"/>
+      <c r="Y770" s="34"/>
+      <c r="Z770" s="34"/>
+      <c r="AA770" s="34"/>
+      <c r="AB770" s="12"/>
+      <c r="AC770" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD770" s="12"/>
+    </row>
+    <row r="771" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A771" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B771" s="29">
+        <v>201010000654</v>
+      </c>
+      <c r="C771" s="28">
+        <v>41418</v>
+      </c>
+      <c r="D771" s="30" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E771" s="31" t="s">
+        <v>572</v>
+      </c>
+      <c r="F771" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G771" s="32">
+        <v>13.27</v>
+      </c>
+      <c r="H771" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="I771" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J771" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K771" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L771" s="35"/>
+      <c r="M771" s="35"/>
+      <c r="N771" s="35"/>
+      <c r="O771" s="35"/>
+      <c r="P771" s="35"/>
+      <c r="Q771" s="35"/>
+      <c r="R771" s="36"/>
+      <c r="S771" s="34"/>
+      <c r="T771" s="37">
+        <v>511.61499433245984</v>
+      </c>
+      <c r="U771" s="34"/>
+      <c r="V771" s="34"/>
+      <c r="W771" s="34"/>
+      <c r="X771" s="34"/>
+      <c r="Y771" s="34"/>
+      <c r="Z771" s="34"/>
+      <c r="AA771" s="34"/>
+      <c r="AB771" s="12"/>
+      <c r="AC771" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD771" s="12"/>
+    </row>
+    <row r="772" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A772" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B772" s="26">
+        <v>221000000718</v>
+      </c>
+      <c r="C772" s="28">
+        <v>41440</v>
+      </c>
+      <c r="D772" s="30" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E772" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="F772" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G772" s="32">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="H772" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="I772" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J772" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K772" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L772" s="35"/>
+      <c r="M772" s="35"/>
+      <c r="N772" s="35"/>
+      <c r="O772" s="35"/>
+      <c r="P772" s="35"/>
+      <c r="Q772" s="35"/>
+      <c r="R772" s="36"/>
+      <c r="S772" s="34"/>
+      <c r="T772" s="37">
+        <v>175.74514288113954</v>
+      </c>
+      <c r="U772" s="34"/>
+      <c r="V772" s="34"/>
+      <c r="W772" s="34"/>
+      <c r="X772" s="34"/>
+      <c r="Y772" s="34"/>
+      <c r="Z772" s="34"/>
+      <c r="AA772" s="34"/>
+      <c r="AB772" s="12"/>
+      <c r="AC772" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD772" s="12"/>
+    </row>
+    <row r="773" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A773" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="B773" s="26">
+        <v>221000000730</v>
+      </c>
+      <c r="C773" s="28">
+        <v>41475</v>
+      </c>
+      <c r="D773" s="30" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E773" s="31" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F773" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G773" s="32">
+        <v>2.262</v>
+      </c>
+      <c r="H773" s="30" t="s">
+        <v>1260</v>
+      </c>
+      <c r="I773" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J773" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K773" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L773" s="35"/>
+      <c r="M773" s="35"/>
+      <c r="N773" s="35"/>
+      <c r="O773" s="35"/>
+      <c r="P773" s="35"/>
+      <c r="Q773" s="35"/>
+      <c r="R773" s="36"/>
+      <c r="S773" s="34"/>
+      <c r="T773" s="37">
+        <v>201.48447445340315</v>
+      </c>
+      <c r="U773" s="34"/>
+      <c r="V773" s="34"/>
+      <c r="W773" s="34"/>
+      <c r="X773" s="34"/>
+      <c r="Y773" s="34"/>
+      <c r="Z773" s="34"/>
+      <c r="AA773" s="34"/>
+      <c r="AB773" s="12"/>
+      <c r="AC773" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD773" s="12"/>
+    </row>
+    <row r="774" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A774" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="B774" s="26">
+        <v>221000000731</v>
+      </c>
+      <c r="C774" s="28">
+        <v>41476</v>
+      </c>
+      <c r="D774" s="30" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E774" s="31" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F774" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G774" s="32">
+        <v>6.5</v>
+      </c>
+      <c r="H774" s="30" t="s">
+        <v>1260</v>
+      </c>
+      <c r="I774" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J774" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K774" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L774" s="35"/>
+      <c r="M774" s="35"/>
+      <c r="N774" s="35"/>
+      <c r="O774" s="35"/>
+      <c r="P774" s="35"/>
+      <c r="Q774" s="35"/>
+      <c r="R774" s="36"/>
+      <c r="S774" s="34"/>
+      <c r="T774" s="37">
+        <v>609.03997295572117</v>
+      </c>
+      <c r="U774" s="34"/>
+      <c r="V774" s="34"/>
+      <c r="W774" s="34"/>
+      <c r="X774" s="34"/>
+      <c r="Y774" s="34"/>
+      <c r="Z774" s="34"/>
+      <c r="AA774" s="34"/>
+      <c r="AB774" s="12"/>
+      <c r="AC774" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD774" s="12"/>
+    </row>
+    <row r="775" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A775" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B775" s="26">
+        <v>201080000086</v>
+      </c>
+      <c r="C775" s="28">
+        <v>41523</v>
+      </c>
+      <c r="D775" s="30" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E775" s="31" t="s">
+        <v>995</v>
+      </c>
+      <c r="F775" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G775" s="32">
+        <v>3.8650000000000002</v>
+      </c>
+      <c r="H775" s="30" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I775" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J775" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K775" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L775" s="35"/>
+      <c r="M775" s="35"/>
+      <c r="N775" s="35"/>
+      <c r="O775" s="35"/>
+      <c r="P775" s="35"/>
+      <c r="Q775" s="35"/>
+      <c r="R775" s="36"/>
+      <c r="S775" s="34"/>
+      <c r="T775" s="37">
+        <v>44.377082656386484</v>
+      </c>
+      <c r="U775" s="34"/>
+      <c r="V775" s="34"/>
+      <c r="W775" s="34"/>
+      <c r="X775" s="34"/>
+      <c r="Y775" s="34"/>
+      <c r="Z775" s="34"/>
+      <c r="AA775" s="34"/>
+      <c r="AB775" s="12"/>
+      <c r="AC775" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD775" s="12"/>
+    </row>
+    <row r="776" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A776" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B776" s="26">
+        <v>221000000541</v>
+      </c>
+      <c r="C776" s="28">
+        <v>41524</v>
+      </c>
+      <c r="D776" s="30" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E776" s="31" t="s">
+        <v>995</v>
+      </c>
+      <c r="F776" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G776" s="32">
+        <v>3.8650000000000002</v>
+      </c>
+      <c r="H776" s="30" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I776" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J776" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K776" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L776" s="35"/>
+      <c r="M776" s="35"/>
+      <c r="N776" s="35"/>
+      <c r="O776" s="35"/>
+      <c r="P776" s="35"/>
+      <c r="Q776" s="35"/>
+      <c r="R776" s="36"/>
+      <c r="S776" s="34"/>
+      <c r="T776" s="37">
+        <v>44.377082656386484</v>
+      </c>
+      <c r="U776" s="34"/>
+      <c r="V776" s="34"/>
+      <c r="W776" s="34"/>
+      <c r="X776" s="34"/>
+      <c r="Y776" s="34"/>
+      <c r="Z776" s="34"/>
+      <c r="AA776" s="34"/>
+      <c r="AB776" s="12"/>
+      <c r="AC776" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD776" s="12"/>
+    </row>
+    <row r="777" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A777" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B777" s="26">
+        <v>201080000096</v>
+      </c>
+      <c r="C777" s="28">
+        <v>41525</v>
+      </c>
+      <c r="D777" s="30" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E777" s="31" t="s">
+        <v>995</v>
+      </c>
+      <c r="F777" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G777" s="32">
+        <v>3.8650000000000002</v>
+      </c>
+      <c r="H777" s="30" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I777" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J777" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K777" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L777" s="35"/>
+      <c r="M777" s="35"/>
+      <c r="N777" s="35"/>
+      <c r="O777" s="35"/>
+      <c r="P777" s="35"/>
+      <c r="Q777" s="35"/>
+      <c r="R777" s="36"/>
+      <c r="S777" s="34"/>
+      <c r="T777" s="37">
+        <v>44.377082656386484</v>
+      </c>
+      <c r="U777" s="34"/>
+      <c r="V777" s="34"/>
+      <c r="W777" s="34"/>
+      <c r="X777" s="34"/>
+      <c r="Y777" s="34"/>
+      <c r="Z777" s="34"/>
+      <c r="AA777" s="34"/>
+      <c r="AB777" s="12"/>
+      <c r="AC777" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD777" s="12"/>
+    </row>
+    <row r="778" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A778" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B778" s="26">
+        <v>221000000740</v>
+      </c>
+      <c r="C778" s="28">
+        <v>41563</v>
+      </c>
+      <c r="D778" s="30" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E778" s="31" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F778" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G778" s="32">
+        <v>2.65</v>
+      </c>
+      <c r="H778" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="I778" s="33" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J778" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K778" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L778" s="35"/>
+      <c r="M778" s="35"/>
+      <c r="N778" s="35"/>
+      <c r="O778" s="35"/>
+      <c r="P778" s="35"/>
+      <c r="Q778" s="35"/>
+      <c r="R778" s="36"/>
+      <c r="S778" s="34"/>
+      <c r="T778" s="37">
+        <v>103.25124180272795</v>
+      </c>
+      <c r="U778" s="34"/>
+      <c r="V778" s="34"/>
+      <c r="W778" s="34"/>
+      <c r="X778" s="34"/>
+      <c r="Y778" s="34"/>
+      <c r="Z778" s="34"/>
+      <c r="AA778" s="34"/>
+      <c r="AB778" s="12"/>
+      <c r="AC778" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD778" s="12"/>
+    </row>
+    <row r="779" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A779" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B779" s="26">
+        <v>221000000180</v>
+      </c>
+      <c r="C779" s="28">
+        <v>41620</v>
+      </c>
+      <c r="D779" s="30" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E779" s="31" t="s">
+        <v>575</v>
+      </c>
+      <c r="F779" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G779" s="32">
+        <v>6.06</v>
+      </c>
+      <c r="H779" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="I779" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J779" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K779" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L779" s="35"/>
+      <c r="M779" s="35"/>
+      <c r="N779" s="35"/>
+      <c r="O779" s="35"/>
+      <c r="P779" s="35"/>
+      <c r="Q779" s="35"/>
+      <c r="R779" s="36"/>
+      <c r="S779" s="34"/>
+      <c r="T779" s="37">
+        <v>135.8491142713163</v>
+      </c>
+      <c r="U779" s="34"/>
+      <c r="V779" s="34"/>
+      <c r="W779" s="34"/>
+      <c r="X779" s="34"/>
+      <c r="Y779" s="34"/>
+      <c r="Z779" s="34"/>
+      <c r="AA779" s="34"/>
+      <c r="AB779" s="12"/>
+      <c r="AC779" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD779" s="12"/>
+    </row>
+    <row r="780" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A780" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B780" s="26">
+        <v>241000000038</v>
+      </c>
+      <c r="C780" s="28">
+        <v>41688</v>
+      </c>
+      <c r="D780" s="30" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E780" s="31" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F780" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G780" s="32">
+        <v>7.2</v>
+      </c>
+      <c r="H780" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="I780" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J780" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K780" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L780" s="35"/>
+      <c r="M780" s="35"/>
+      <c r="N780" s="35"/>
+      <c r="O780" s="35"/>
+      <c r="P780" s="35"/>
+      <c r="Q780" s="35"/>
+      <c r="R780" s="36"/>
+      <c r="S780" s="34"/>
+      <c r="T780" s="37">
+        <v>2340.1136682120541</v>
+      </c>
+      <c r="U780" s="34"/>
+      <c r="V780" s="34"/>
+      <c r="W780" s="34"/>
+      <c r="X780" s="34"/>
+      <c r="Y780" s="34"/>
+      <c r="Z780" s="34"/>
+      <c r="AA780" s="34"/>
+      <c r="AB780" s="12"/>
+      <c r="AC780" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD780" s="12"/>
+    </row>
+    <row r="781" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A781" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B781" s="26">
+        <v>251000000060.40601</v>
+      </c>
+      <c r="C781" s="27">
+        <v>41807</v>
+      </c>
+      <c r="D781" s="30" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E781" s="31" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F781" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G781" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="H781" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="I781" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J781" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K781" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L781" s="35"/>
+      <c r="M781" s="35"/>
+      <c r="N781" s="35"/>
+      <c r="O781" s="35"/>
+      <c r="P781" s="35"/>
+      <c r="Q781" s="35"/>
+      <c r="R781" s="36"/>
+      <c r="S781" s="34"/>
+      <c r="T781" s="37">
+        <v>344.22611015924207</v>
+      </c>
+      <c r="U781" s="34"/>
+      <c r="V781" s="34"/>
+      <c r="W781" s="34"/>
+      <c r="X781" s="34"/>
+      <c r="Y781" s="34"/>
+      <c r="Z781" s="34"/>
+      <c r="AA781" s="34"/>
+      <c r="AB781" s="12"/>
+      <c r="AC781" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD781" s="12"/>
+    </row>
+    <row r="782" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A782" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="B782" s="26">
+        <v>999999999999</v>
+      </c>
+      <c r="C782" s="28">
+        <v>41838</v>
+      </c>
+      <c r="D782" s="30" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E782" s="31" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F782" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G782" s="32">
+        <v>10.4</v>
+      </c>
+      <c r="H782" s="30" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I782" s="33" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J782" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K782" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L782" s="35"/>
+      <c r="M782" s="35"/>
+      <c r="N782" s="35"/>
+      <c r="O782" s="35"/>
+      <c r="P782" s="35"/>
+      <c r="Q782" s="35"/>
+      <c r="R782" s="36"/>
+      <c r="S782" s="34"/>
+      <c r="T782" s="37">
+        <v>211.6925134</v>
+      </c>
+      <c r="U782" s="34"/>
+      <c r="V782" s="34"/>
+      <c r="W782" s="34"/>
+      <c r="X782" s="34"/>
+      <c r="Y782" s="34"/>
+      <c r="Z782" s="34"/>
+      <c r="AA782" s="34"/>
+      <c r="AB782" s="12"/>
+      <c r="AC782" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD782" s="12"/>
+    </row>
+    <row r="783" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A783" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B783" s="26">
+        <v>221000000404</v>
+      </c>
+      <c r="C783" s="27">
+        <v>41948</v>
+      </c>
+      <c r="D783" s="30" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E783" s="31" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F783" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G783" s="32">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H783" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="I783" s="33" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J783" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K783" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L783" s="35"/>
+      <c r="M783" s="35"/>
+      <c r="N783" s="35"/>
+      <c r="O783" s="35"/>
+      <c r="P783" s="35"/>
+      <c r="Q783" s="35"/>
+      <c r="R783" s="36"/>
+      <c r="S783" s="34"/>
+      <c r="T783" s="37">
+        <v>267.65598998857757</v>
+      </c>
+      <c r="U783" s="34"/>
+      <c r="V783" s="34"/>
+      <c r="W783" s="34"/>
+      <c r="X783" s="34"/>
+      <c r="Y783" s="34"/>
+      <c r="Z783" s="34"/>
+      <c r="AA783" s="34"/>
+      <c r="AB783" s="12"/>
+      <c r="AC783" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD783" s="12"/>
+    </row>
+    <row r="784" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A784" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B784" s="26">
+        <v>241000000044</v>
+      </c>
+      <c r="C784" s="28">
+        <v>41962</v>
+      </c>
+      <c r="D784" s="30" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E784" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F784" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G784" s="32">
+        <v>22.84</v>
+      </c>
+      <c r="H784" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="I784" s="33" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J784" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K784" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L784" s="35"/>
+      <c r="M784" s="35"/>
+      <c r="N784" s="35"/>
+      <c r="O784" s="35"/>
+      <c r="P784" s="35"/>
+      <c r="Q784" s="35"/>
+      <c r="R784" s="36"/>
+      <c r="S784" s="34"/>
+      <c r="T784" s="37">
+        <v>161.13743510227272</v>
+      </c>
+      <c r="U784" s="34"/>
+      <c r="V784" s="34"/>
+      <c r="W784" s="34"/>
+      <c r="X784" s="34"/>
+      <c r="Y784" s="34"/>
+      <c r="Z784" s="34"/>
+      <c r="AA784" s="34"/>
+      <c r="AB784" s="12"/>
+      <c r="AC784" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD784" s="12"/>
+    </row>
+    <row r="785" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A785" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B785" s="26">
+        <v>221000000395</v>
+      </c>
+      <c r="C785" s="27">
+        <v>41963</v>
+      </c>
+      <c r="D785" s="30" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E785" s="31" t="s">
+        <v>855</v>
+      </c>
+      <c r="F785" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G785" s="32">
+        <v>6.3</v>
+      </c>
+      <c r="H785" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="I785" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J785" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K785" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L785" s="35"/>
+      <c r="M785" s="35"/>
+      <c r="N785" s="35"/>
+      <c r="O785" s="35"/>
+      <c r="P785" s="35"/>
+      <c r="Q785" s="35"/>
+      <c r="R785" s="36"/>
+      <c r="S785" s="34"/>
+      <c r="T785" s="37">
+        <v>157.72192088288651</v>
+      </c>
+      <c r="U785" s="34"/>
+      <c r="V785" s="34"/>
+      <c r="W785" s="34"/>
+      <c r="X785" s="34"/>
+      <c r="Y785" s="34"/>
+      <c r="Z785" s="34"/>
+      <c r="AA785" s="34"/>
+      <c r="AB785" s="12"/>
+      <c r="AC785" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD785" s="12"/>
+    </row>
+    <row r="786" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A786" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B786" s="26">
+        <v>221000000399</v>
+      </c>
+      <c r="C786" s="28">
+        <v>41965</v>
+      </c>
+      <c r="D786" s="30" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E786" s="31" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F786" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G786" s="32">
+        <v>6.05</v>
+      </c>
+      <c r="H786" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="I786" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J786" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K786" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L786" s="35"/>
+      <c r="M786" s="35"/>
+      <c r="N786" s="35"/>
+      <c r="O786" s="35"/>
+      <c r="P786" s="35"/>
+      <c r="Q786" s="35"/>
+      <c r="R786" s="36"/>
+      <c r="S786" s="34"/>
+      <c r="T786" s="37">
+        <v>135.83615096082781</v>
+      </c>
+      <c r="U786" s="34"/>
+      <c r="V786" s="34"/>
+      <c r="W786" s="34"/>
+      <c r="X786" s="34"/>
+      <c r="Y786" s="34"/>
+      <c r="Z786" s="34"/>
+      <c r="AA786" s="34"/>
+      <c r="AB786" s="12"/>
+      <c r="AC786" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD786" s="12"/>
+    </row>
+    <row r="787" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A787" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B787" s="26">
+        <v>241000000045</v>
+      </c>
+      <c r="C787" s="27">
+        <v>41984</v>
+      </c>
+      <c r="D787" s="30" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E787" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="F787" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G787" s="32">
+        <v>5.84</v>
+      </c>
+      <c r="H787" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="I787" s="33" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J787" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K787" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L787" s="35"/>
+      <c r="M787" s="35"/>
+      <c r="N787" s="35"/>
+      <c r="O787" s="35"/>
+      <c r="P787" s="35"/>
+      <c r="Q787" s="35"/>
+      <c r="R787" s="36"/>
+      <c r="S787" s="34"/>
+      <c r="T787" s="37">
+        <v>1367.1922893771416</v>
+      </c>
+      <c r="U787" s="34"/>
+      <c r="V787" s="34"/>
+      <c r="W787" s="34"/>
+      <c r="X787" s="34"/>
+      <c r="Y787" s="34"/>
+      <c r="Z787" s="34"/>
+      <c r="AA787" s="34"/>
+      <c r="AB787" s="12"/>
+      <c r="AC787" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD787" s="12"/>
+    </row>
+    <row r="788" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A788" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B788" s="26">
+        <v>221000000418</v>
+      </c>
+      <c r="C788" s="27">
+        <v>42049</v>
+      </c>
+      <c r="D788" s="30" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E788" s="31" t="s">
+        <v>688</v>
+      </c>
+      <c r="F788" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G788" s="32">
+        <v>4.2</v>
+      </c>
+      <c r="H788" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="I788" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J788" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K788" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L788" s="35"/>
+      <c r="M788" s="35"/>
+      <c r="N788" s="35"/>
+      <c r="O788" s="35"/>
+      <c r="P788" s="35"/>
+      <c r="Q788" s="35"/>
+      <c r="R788" s="36"/>
+      <c r="S788" s="34"/>
+      <c r="T788" s="37">
+        <v>345.68776113686755</v>
+      </c>
+      <c r="U788" s="34"/>
+      <c r="V788" s="34"/>
+      <c r="W788" s="34"/>
+      <c r="X788" s="34"/>
+      <c r="Y788" s="34"/>
+      <c r="Z788" s="34"/>
+      <c r="AA788" s="34"/>
+      <c r="AB788" s="12"/>
+      <c r="AC788" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD788" s="12"/>
+    </row>
+    <row r="789" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A789" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B789" s="26">
+        <v>221000000392</v>
+      </c>
+      <c r="C789" s="27">
+        <v>42064</v>
+      </c>
+      <c r="D789" s="30" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E789" s="31" t="s">
+        <v>705</v>
+      </c>
+      <c r="F789" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G789" s="32">
+        <v>3.2240000000000002</v>
+      </c>
+      <c r="H789" s="30" t="s">
+        <v>846</v>
+      </c>
+      <c r="I789" s="33" t="s">
+        <v>1219</v>
+      </c>
+      <c r="J789" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K789" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L789" s="35"/>
+      <c r="M789" s="35"/>
+      <c r="N789" s="35"/>
+      <c r="O789" s="35"/>
+      <c r="P789" s="35"/>
+      <c r="Q789" s="35"/>
+      <c r="R789" s="36"/>
+      <c r="S789" s="34"/>
+      <c r="T789" s="37">
+        <v>185.37351764294831</v>
+      </c>
+      <c r="U789" s="34"/>
+      <c r="V789" s="34"/>
+      <c r="W789" s="34"/>
+      <c r="X789" s="34"/>
+      <c r="Y789" s="34"/>
+      <c r="Z789" s="34"/>
+      <c r="AA789" s="34"/>
+      <c r="AB789" s="12"/>
+      <c r="AC789" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD789" s="12"/>
+    </row>
+    <row r="790" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A790" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B790" s="26">
+        <v>221000000425</v>
+      </c>
+      <c r="C790" s="27">
+        <v>42076</v>
+      </c>
+      <c r="D790" s="30" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E790" s="31" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F790" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G790" s="32">
+        <v>18.34</v>
+      </c>
+      <c r="H790" s="30" t="s">
+        <v>606</v>
+      </c>
+      <c r="I790" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J790" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K790" s="33" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L790" s="35"/>
+      <c r="M790" s="35"/>
+      <c r="N790" s="35"/>
+      <c r="O790" s="35"/>
+      <c r="P790" s="35"/>
+      <c r="Q790" s="35"/>
+      <c r="R790" s="36"/>
+      <c r="S790" s="34"/>
+      <c r="T790" s="37">
+        <v>675.3458786309883</v>
+      </c>
+      <c r="U790" s="34"/>
+      <c r="V790" s="34"/>
+      <c r="W790" s="34"/>
+      <c r="X790" s="34"/>
+      <c r="Y790" s="34"/>
+      <c r="Z790" s="34"/>
+      <c r="AA790" s="34"/>
+      <c r="AB790" s="12"/>
+      <c r="AC790" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AD790" s="12"/>
+    </row>
+    <row r="791" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A791" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B791" s="26" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C791" s="27" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D791" s="30" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E791" s="31"/>
+      <c r="F791" s="26"/>
+    </row>
+    <row r="792" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A792" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B792" s="26" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C792" s="27" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D792" s="30" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E792" s="31"/>
+      <c r="F792" s="26"/>
+    </row>
+    <row r="793" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A793" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B793" s="26" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C793" s="27" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D793" s="30" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E793" s="31"/>
+      <c r="F793" s="26"/>
+    </row>
+    <row r="794" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A794" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B794" s="26" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C794" s="27" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D794" s="30" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E794" s="31"/>
+      <c r="F794" s="26"/>
+    </row>
+    <row r="795" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A795" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B795" s="26" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C795" s="27" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D795" s="30" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E795" s="31"/>
+      <c r="F795" s="26"/>
+    </row>
+    <row r="796" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A796" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B796" s="26" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C796" s="27" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D796" s="30" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E796" s="31"/>
+      <c r="F796" s="26"/>
+    </row>
+    <row r="797" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A797" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B797" s="26" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C797" s="27" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D797" s="30" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E797" s="31"/>
+      <c r="F797" s="26"/>
+    </row>
+    <row r="798" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A798" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B798" s="26" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C798" s="27" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D798" s="30" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E798" s="31"/>
+      <c r="F798" s="26"/>
+    </row>
+    <row r="799" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A799" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B799" s="26" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C799" s="27" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D799" s="30" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E799" s="31"/>
+      <c r="F799" s="26"/>
+    </row>
+    <row r="800" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A800" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B800" s="26" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C800" s="27" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D800" s="30" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E800" s="31"/>
+      <c r="F800" s="26"/>
+    </row>
+    <row r="801" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A801" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B801" s="26" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C801" s="27" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D801" s="30" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E801" s="31"/>
+      <c r="F801" s="26"/>
+    </row>
+    <row r="802" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A802" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B802" s="26" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C802" s="27" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D802" s="30" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E802" s="31"/>
+      <c r="F802" s="26"/>
+    </row>
+    <row r="803" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A803" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B803" s="26" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C803" s="27" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D803" s="30" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E803" s="31"/>
+      <c r="F803" s="26"/>
+    </row>
+    <row r="804" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A804" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B804" s="26" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C804" s="27" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D804" s="30" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E804" s="31"/>
+      <c r="F804" s="26"/>
+    </row>
+    <row r="805" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A805" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B805" s="26"/>
+      <c r="C805" s="27"/>
+      <c r="D805" s="30" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E805" s="31"/>
+      <c r="F805" s="26"/>
+    </row>
+    <row r="806" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A806" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B806" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C806" s="27"/>
+      <c r="D806" s="30" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E806" s="31"/>
+      <c r="F806" s="26"/>
+    </row>
+    <row r="807" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A807" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B807" s="26" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C807" s="27"/>
+      <c r="D807" s="30" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E807" s="31"/>
+      <c r="F807" s="26"/>
+    </row>
+    <row r="808" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A808" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B808" s="26" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C808" s="27"/>
+      <c r="D808" s="30" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E808" s="31"/>
+      <c r="F808" s="26"/>
+    </row>
+    <row r="809" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A809" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B809" s="26"/>
+      <c r="C809" s="27"/>
+      <c r="D809" s="30" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E809" s="31"/>
+      <c r="F809" s="26"/>
+    </row>
+    <row r="810" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A810" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B810" s="26" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C810" s="27"/>
+      <c r="D810" s="30" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E810" s="31"/>
+      <c r="F810" s="26"/>
+    </row>
+    <row r="811" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A811" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B811" s="26" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C811" s="27"/>
+      <c r="D811" s="30" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E811" s="31"/>
+      <c r="F811" s="26"/>
+    </row>
+    <row r="812" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A812" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B812" s="26" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C812" s="27"/>
+      <c r="D812" s="30" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E812" s="31"/>
+      <c r="F812" s="26"/>
+    </row>
+    <row r="813" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A813" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B813" s="26" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C813" s="27"/>
+      <c r="D813" s="30" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E813" s="31"/>
+      <c r="F813" s="26"/>
+    </row>
+    <row r="814" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A814" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B814" s="26"/>
+      <c r="C814" s="27"/>
+      <c r="D814" s="30" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E814" s="31"/>
+      <c r="F814" s="26"/>
+    </row>
+    <row r="815" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A815" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B815" s="26"/>
+      <c r="C815" s="27"/>
+      <c r="D815" s="30" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E815" s="31"/>
+      <c r="F815" s="26"/>
+    </row>
+    <row r="816" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A816" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B816" s="26" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C816" s="27"/>
+      <c r="D816" s="30" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E816" s="31"/>
+      <c r="F816" s="26"/>
+    </row>
+    <row r="817" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A817" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B817" s="26"/>
+      <c r="C817" s="27"/>
+      <c r="D817" s="30" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E817" s="31"/>
+      <c r="F817" s="26"/>
+    </row>
+    <row r="818" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A818" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B818" s="26" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C818" s="27"/>
+      <c r="D818" s="30" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E818" s="31"/>
+      <c r="F818" s="26"/>
+    </row>
+    <row r="819" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A819" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B819" s="26" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C819" s="27"/>
+      <c r="D819" s="30" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E819" s="31"/>
+      <c r="F819" s="26"/>
+    </row>
+    <row r="820" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A820" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B820" s="26" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C820" s="27"/>
+      <c r="D820" s="30" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E820" s="31"/>
+      <c r="F820" s="26"/>
+    </row>
+    <row r="821" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A821" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B821" s="26"/>
+      <c r="C821" s="27"/>
+      <c r="D821" s="30" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E821" s="31"/>
+      <c r="F821" s="26"/>
+    </row>
+    <row r="822" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A822" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B822" s="26"/>
+      <c r="C822" s="27"/>
+      <c r="D822" s="30" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E822" s="31"/>
+      <c r="F822" s="26"/>
+    </row>
+    <row r="823" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A823" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B823" s="26" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C823" s="27"/>
+      <c r="D823" s="30" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E823" s="31"/>
+      <c r="F823" s="26"/>
+    </row>
+    <row r="824" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A824" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B824" s="26" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C824" s="27"/>
+      <c r="D824" s="30" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E824" s="31"/>
+      <c r="F824" s="26"/>
+    </row>
+    <row r="825" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A825" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B825" s="26"/>
+      <c r="C825" s="27"/>
+      <c r="D825" s="30" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E825" s="31"/>
+      <c r="F825" s="26"/>
+    </row>
+    <row r="826" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A826" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B826" s="26" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C826" s="27"/>
+      <c r="D826" s="30" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E826" s="31"/>
+      <c r="F826" s="26"/>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D791:D804">
+    <sortCondition ref="D791:D804"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Hyperlink_test xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Hyperlink_test>
-    <file_location xmlns="3a1b5eaf-929c-4573-820b-891dab44de53" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003038969B0484BC4CA3D2193B8D466837" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a7d958e08c55628ca432b8bed74f23d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xmlns:ns3="3a1b5eaf-929c-4573-820b-891dab44de53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0851d0c4117cb1b37bf320fb4a56d55a" ns2:_="" ns3:_="">
     <xsd:import namespace="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
@@ -70927,26 +74533,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{463DA1DB-F675-4EF1-9714-953AFC05288A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
-    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Hyperlink_test xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Hyperlink_test>
+    <file_location xmlns="3a1b5eaf-929c-4573-820b-891dab44de53" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCEC1A57-4DA5-4CC2-ABE5-6030A064E48B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ECD1D35-0CAC-433E-A5D6-3D3C549F3634}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -70963,4 +74575,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{463DA1DB-F675-4EF1-9714-953AFC05288A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
+    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCEC1A57-4DA5-4CC2-ABE5-6030A064E48B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/BKQBF_TAB-6.xlsx
+++ b/BKQBF_TAB-6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{E45ECF03-8BBF-43CE-AC78-00B76E360356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC8426AD-DFB6-4BBF-BC22-BF7933DC6C11}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{E45ECF03-8BBF-43CE-AC78-00B76E360356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C6FD17-BD76-423B-BB50-341AC7C08655}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1AA8A838-AA6C-419E-91A0-2F2725546F0E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7244" uniqueCount="1357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7258" uniqueCount="1355">
   <si>
     <t>Tipologia</t>
   </si>
@@ -4014,12 +4014,6 @@
   </si>
   <si>
     <t>7210480</t>
-  </si>
-  <si>
-    <t>9013</t>
-  </si>
-  <si>
-    <t>9014</t>
   </si>
   <si>
     <t>241000000099</t>
@@ -4185,7 +4179,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4219,6 +4213,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4321,7 +4321,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4426,6 +4426,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="7" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -73756,88 +73759,98 @@
       <c r="A791" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B791" s="26" t="s">
-        <v>1299</v>
+      <c r="B791" s="26">
+        <v>231000000001</v>
       </c>
       <c r="C791" s="27" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D791" s="30" t="s">
         <v>1291</v>
       </c>
-      <c r="E791" s="31"/>
+      <c r="E791" s="38" t="s">
+        <v>1299</v>
+      </c>
       <c r="F791" s="26"/>
     </row>
     <row r="792" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B792" s="26" t="s">
-        <v>1299</v>
+      <c r="B792" s="26">
+        <v>231000000001</v>
       </c>
       <c r="C792" s="27" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D792" s="30" t="s">
         <v>1285</v>
       </c>
-      <c r="E792" s="31"/>
+      <c r="E792" s="38" t="s">
+        <v>1299</v>
+      </c>
       <c r="F792" s="26"/>
     </row>
     <row r="793" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B793" s="26" t="s">
-        <v>1307</v>
+      <c r="B793" s="26">
+        <v>231000000002</v>
       </c>
       <c r="C793" s="27" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="D793" s="30" t="s">
         <v>1295</v>
       </c>
-      <c r="E793" s="31"/>
+      <c r="E793" s="38" t="s">
+        <v>1307</v>
+      </c>
       <c r="F793" s="26"/>
     </row>
     <row r="794" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B794" s="26" t="s">
-        <v>1307</v>
+      <c r="B794" s="26">
+        <v>231000000002</v>
       </c>
       <c r="C794" s="27" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D794" s="30" t="s">
         <v>1289</v>
       </c>
-      <c r="E794" s="31"/>
+      <c r="E794" s="38" t="s">
+        <v>1307</v>
+      </c>
       <c r="F794" s="26"/>
     </row>
     <row r="795" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B795" s="26" t="s">
-        <v>1331</v>
+      <c r="B795" s="26">
+        <v>231000000003</v>
       </c>
       <c r="C795" s="27" t="s">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="D795" s="30" t="s">
         <v>1296</v>
       </c>
-      <c r="E795" s="31"/>
+      <c r="E795" s="38" t="s">
+        <v>1329</v>
+      </c>
       <c r="F795" s="26"/>
     </row>
     <row r="796" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B796" s="26" t="s">
-        <v>1331</v>
+      <c r="B796" s="26">
+        <v>231000000003</v>
       </c>
       <c r="C796" s="27" t="s">
         <v>1318</v>
@@ -73845,7 +73858,9 @@
       <c r="D796" s="30" t="s">
         <v>1290</v>
       </c>
-      <c r="E796" s="31"/>
+      <c r="E796" s="38" t="s">
+        <v>1329</v>
+      </c>
       <c r="F796" s="26"/>
     </row>
     <row r="797" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73853,23 +73868,23 @@
         <v>26</v>
       </c>
       <c r="B797" s="26" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C797" s="27" t="s">
-        <v>1319</v>
-      </c>
+        <v>1351</v>
+      </c>
+      <c r="C797" s="27"/>
       <c r="D797" s="30" t="s">
         <v>1298</v>
       </c>
-      <c r="E797" s="31"/>
+      <c r="E797" s="38" t="s">
+        <v>1351</v>
+      </c>
       <c r="F797" s="26"/>
     </row>
     <row r="798" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B798" s="26" t="s">
-        <v>1337</v>
+      <c r="B798" s="26">
+        <v>231000000004</v>
       </c>
       <c r="C798" s="27" t="s">
         <v>1320</v>
@@ -73877,55 +73892,63 @@
       <c r="D798" s="30" t="s">
         <v>1292</v>
       </c>
-      <c r="E798" s="31"/>
+      <c r="E798" s="38" t="s">
+        <v>1335</v>
+      </c>
       <c r="F798" s="26"/>
     </row>
     <row r="799" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B799" s="26" t="s">
-        <v>1337</v>
+      <c r="B799" s="26">
+        <v>231000000004</v>
       </c>
       <c r="C799" s="27" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="D799" s="30" t="s">
         <v>1286</v>
       </c>
-      <c r="E799" s="31"/>
+      <c r="E799" s="38" t="s">
+        <v>1335</v>
+      </c>
       <c r="F799" s="26"/>
     </row>
     <row r="800" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B800" s="26" t="s">
-        <v>1345</v>
+      <c r="B800" s="26">
+        <v>231000000005</v>
       </c>
       <c r="C800" s="27" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="D800" s="30" t="s">
         <v>1293</v>
       </c>
-      <c r="E800" s="31"/>
+      <c r="E800" s="38" t="s">
+        <v>1343</v>
+      </c>
       <c r="F800" s="26"/>
     </row>
     <row r="801" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B801" s="26" t="s">
-        <v>1345</v>
+      <c r="B801" s="26">
+        <v>231000000005</v>
       </c>
       <c r="C801" s="27" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
       <c r="D801" s="30" t="s">
         <v>1287</v>
       </c>
-      <c r="E801" s="31"/>
+      <c r="E801" s="38" t="s">
+        <v>1343</v>
+      </c>
       <c r="F801" s="26"/>
     </row>
     <row r="802" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73933,47 +73956,51 @@
         <v>26</v>
       </c>
       <c r="B802" s="26" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C802" s="27" t="s">
-        <v>1324</v>
-      </c>
+        <v>1345</v>
+      </c>
+      <c r="C802" s="27"/>
       <c r="D802" s="30" t="s">
         <v>1297</v>
       </c>
-      <c r="E802" s="31"/>
+      <c r="E802" s="38" t="s">
+        <v>1345</v>
+      </c>
       <c r="F802" s="26"/>
     </row>
     <row r="803" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B803" s="26" t="s">
-        <v>1333</v>
+      <c r="B803" s="26">
+        <v>231000000007</v>
       </c>
       <c r="C803" s="27" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="D803" s="30" t="s">
         <v>1294</v>
       </c>
-      <c r="E803" s="31"/>
+      <c r="E803" s="38" t="s">
+        <v>1331</v>
+      </c>
       <c r="F803" s="26"/>
     </row>
     <row r="804" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B804" s="26" t="s">
-        <v>1333</v>
+      <c r="B804" s="26">
+        <v>231000000007</v>
       </c>
       <c r="C804" s="27" t="s">
-        <v>1326</v>
+        <v>1316</v>
       </c>
       <c r="D804" s="30" t="s">
         <v>1288</v>
       </c>
-      <c r="E804" s="31"/>
+      <c r="E804" s="38" t="s">
+        <v>1331</v>
+      </c>
       <c r="F804" s="26"/>
     </row>
     <row r="805" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73985,7 +74012,7 @@
       <c r="D805" s="30" t="s">
         <v>1300</v>
       </c>
-      <c r="E805" s="31"/>
+      <c r="E805" s="38"/>
       <c r="F805" s="26"/>
     </row>
     <row r="806" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73999,7 +74026,9 @@
       <c r="D806" s="30" t="s">
         <v>1302</v>
       </c>
-      <c r="E806" s="31"/>
+      <c r="E806" s="38" t="s">
+        <v>1301</v>
+      </c>
       <c r="F806" s="26"/>
     </row>
     <row r="807" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74013,7 +74042,9 @@
       <c r="D807" s="30" t="s">
         <v>1304</v>
       </c>
-      <c r="E807" s="31"/>
+      <c r="E807" s="38" t="s">
+        <v>1303</v>
+      </c>
       <c r="F807" s="26"/>
     </row>
     <row r="808" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74027,7 +74058,9 @@
       <c r="D808" s="30" t="s">
         <v>1306</v>
       </c>
-      <c r="E808" s="31"/>
+      <c r="E808" s="38" t="s">
+        <v>1305</v>
+      </c>
       <c r="F808" s="26"/>
     </row>
     <row r="809" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74039,7 +74072,7 @@
       <c r="D809" s="30" t="s">
         <v>1308</v>
       </c>
-      <c r="E809" s="31"/>
+      <c r="E809" s="38"/>
       <c r="F809" s="26"/>
     </row>
     <row r="810" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74053,7 +74086,9 @@
       <c r="D810" s="30" t="s">
         <v>1310</v>
       </c>
-      <c r="E810" s="31"/>
+      <c r="E810" s="38" t="s">
+        <v>1309</v>
+      </c>
       <c r="F810" s="26"/>
     </row>
     <row r="811" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74067,7 +74102,9 @@
       <c r="D811" s="30" t="s">
         <v>1312</v>
       </c>
-      <c r="E811" s="31"/>
+      <c r="E811" s="38" t="s">
+        <v>1311</v>
+      </c>
       <c r="F811" s="26"/>
     </row>
     <row r="812" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74075,13 +74112,15 @@
         <v>26</v>
       </c>
       <c r="B812" s="26" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C812" s="27"/>
       <c r="D812" s="30" t="s">
-        <v>1328</v>
-      </c>
-      <c r="E812" s="31"/>
+        <v>1326</v>
+      </c>
+      <c r="E812" s="38" t="s">
+        <v>1325</v>
+      </c>
       <c r="F812" s="26"/>
     </row>
     <row r="813" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74089,13 +74128,15 @@
         <v>26</v>
       </c>
       <c r="B813" s="26" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C813" s="27"/>
       <c r="D813" s="30" t="s">
-        <v>1330</v>
-      </c>
-      <c r="E813" s="31"/>
+        <v>1328</v>
+      </c>
+      <c r="E813" s="38" t="s">
+        <v>1327</v>
+      </c>
       <c r="F813" s="26"/>
     </row>
     <row r="814" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74105,9 +74146,9 @@
       <c r="B814" s="26"/>
       <c r="C814" s="27"/>
       <c r="D814" s="30" t="s">
-        <v>1332</v>
-      </c>
-      <c r="E814" s="31"/>
+        <v>1330</v>
+      </c>
+      <c r="E814" s="38"/>
       <c r="F814" s="26"/>
     </row>
     <row r="815" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74117,9 +74158,9 @@
       <c r="B815" s="26"/>
       <c r="C815" s="27"/>
       <c r="D815" s="30" t="s">
-        <v>1334</v>
-      </c>
-      <c r="E815" s="31"/>
+        <v>1332</v>
+      </c>
+      <c r="E815" s="38"/>
       <c r="F815" s="26"/>
     </row>
     <row r="816" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74127,13 +74168,15 @@
         <v>26</v>
       </c>
       <c r="B816" s="26" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C816" s="27"/>
       <c r="D816" s="30" t="s">
-        <v>1336</v>
-      </c>
-      <c r="E816" s="31"/>
+        <v>1334</v>
+      </c>
+      <c r="E816" s="38" t="s">
+        <v>1333</v>
+      </c>
       <c r="F816" s="26"/>
     </row>
     <row r="817" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74143,9 +74186,9 @@
       <c r="B817" s="26"/>
       <c r="C817" s="27"/>
       <c r="D817" s="30" t="s">
-        <v>1338</v>
-      </c>
-      <c r="E817" s="31"/>
+        <v>1336</v>
+      </c>
+      <c r="E817" s="38"/>
       <c r="F817" s="26"/>
     </row>
     <row r="818" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74153,13 +74196,15 @@
         <v>26</v>
       </c>
       <c r="B818" s="26" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C818" s="27"/>
       <c r="D818" s="30" t="s">
-        <v>1340</v>
-      </c>
-      <c r="E818" s="31"/>
+        <v>1338</v>
+      </c>
+      <c r="E818" s="38" t="s">
+        <v>1337</v>
+      </c>
       <c r="F818" s="26"/>
     </row>
     <row r="819" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74167,13 +74212,15 @@
         <v>26</v>
       </c>
       <c r="B819" s="26" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C819" s="27"/>
       <c r="D819" s="30" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E819" s="31"/>
+        <v>1340</v>
+      </c>
+      <c r="E819" s="38" t="s">
+        <v>1339</v>
+      </c>
       <c r="F819" s="26"/>
     </row>
     <row r="820" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74181,13 +74228,15 @@
         <v>26</v>
       </c>
       <c r="B820" s="26" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C820" s="27"/>
       <c r="D820" s="30" t="s">
-        <v>1344</v>
-      </c>
-      <c r="E820" s="31"/>
+        <v>1342</v>
+      </c>
+      <c r="E820" s="38" t="s">
+        <v>1341</v>
+      </c>
       <c r="F820" s="26"/>
     </row>
     <row r="821" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74197,9 +74246,9 @@
       <c r="B821" s="26"/>
       <c r="C821" s="27"/>
       <c r="D821" s="30" t="s">
-        <v>1346</v>
-      </c>
-      <c r="E821" s="31"/>
+        <v>1344</v>
+      </c>
+      <c r="E821" s="38"/>
       <c r="F821" s="26"/>
     </row>
     <row r="822" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74209,9 +74258,9 @@
       <c r="B822" s="26"/>
       <c r="C822" s="27"/>
       <c r="D822" s="30" t="s">
-        <v>1348</v>
-      </c>
-      <c r="E822" s="31"/>
+        <v>1346</v>
+      </c>
+      <c r="E822" s="38"/>
       <c r="F822" s="26"/>
     </row>
     <row r="823" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74219,13 +74268,15 @@
         <v>26</v>
       </c>
       <c r="B823" s="26" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C823" s="27"/>
       <c r="D823" s="30" t="s">
-        <v>1350</v>
-      </c>
-      <c r="E823" s="31"/>
+        <v>1348</v>
+      </c>
+      <c r="E823" s="38" t="s">
+        <v>1347</v>
+      </c>
       <c r="F823" s="26"/>
     </row>
     <row r="824" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74233,13 +74284,15 @@
         <v>26</v>
       </c>
       <c r="B824" s="26" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C824" s="27"/>
       <c r="D824" s="30" t="s">
-        <v>1352</v>
-      </c>
-      <c r="E824" s="31"/>
+        <v>1350</v>
+      </c>
+      <c r="E824" s="38" t="s">
+        <v>1349</v>
+      </c>
       <c r="F824" s="26"/>
     </row>
     <row r="825" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74249,9 +74302,9 @@
       <c r="B825" s="26"/>
       <c r="C825" s="27"/>
       <c r="D825" s="30" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E825" s="31"/>
+        <v>1352</v>
+      </c>
+      <c r="E825" s="38"/>
       <c r="F825" s="26"/>
     </row>
     <row r="826" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74259,13 +74312,15 @@
         <v>26</v>
       </c>
       <c r="B826" s="26" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C826" s="27"/>
       <c r="D826" s="30" t="s">
-        <v>1356</v>
-      </c>
-      <c r="E826" s="31"/>
+        <v>1354</v>
+      </c>
+      <c r="E826" s="38" t="s">
+        <v>1353</v>
+      </c>
       <c r="F826" s="26"/>
     </row>
   </sheetData>
@@ -74278,6 +74333,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Hyperlink_test xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Hyperlink_test>
+    <file_location xmlns="3a1b5eaf-929c-4573-820b-891dab44de53" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003038969B0484BC4CA3D2193B8D466837" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a7d958e08c55628ca432b8bed74f23d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xmlns:ns3="3a1b5eaf-929c-4573-820b-891dab44de53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0851d0c4117cb1b37bf320fb4a56d55a" ns2:_="" ns3:_="">
     <xsd:import namespace="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
@@ -74533,32 +74613,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Hyperlink_test xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Hyperlink_test>
-    <file_location xmlns="3a1b5eaf-929c-4573-820b-891dab44de53" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCEC1A57-4DA5-4CC2-ABE5-6030A064E48B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{463DA1DB-F675-4EF1-9714-953AFC05288A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
+    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ECD1D35-0CAC-433E-A5D6-3D3C549F3634}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -74575,23 +74649,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{463DA1DB-F675-4EF1-9714-953AFC05288A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
-    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCEC1A57-4DA5-4CC2-ABE5-6030A064E48B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/BKQBF_TAB-6.xlsx
+++ b/BKQBF_TAB-6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{E45ECF03-8BBF-43CE-AC78-00B76E360356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C6FD17-BD76-423B-BB50-341AC7C08655}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{E45ECF03-8BBF-43CE-AC78-00B76E360356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{255C17AE-F086-4107-878F-60C81793A4FE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1AA8A838-AA6C-419E-91A0-2F2725546F0E}"/>
   </bookViews>
@@ -4804,7 +4804,7 @@
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="16" customWidth="1"/>
-    <col min="2" max="2" width="13" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="16" customWidth="1"/>
     <col min="3" max="3" width="10.140625" style="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="43.140625" style="17" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" style="18" customWidth="1" outlineLevel="1"/>
@@ -73778,7 +73778,7 @@
         <v>26</v>
       </c>
       <c r="B792" s="26">
-        <v>231000000001</v>
+        <v>2310000000012</v>
       </c>
       <c r="C792" s="27" t="s">
         <v>1313</v>
@@ -73814,7 +73814,7 @@
         <v>26</v>
       </c>
       <c r="B794" s="26">
-        <v>231000000002</v>
+        <v>2310000000022</v>
       </c>
       <c r="C794" s="27" t="s">
         <v>1317</v>
@@ -73850,7 +73850,7 @@
         <v>26</v>
       </c>
       <c r="B796" s="26">
-        <v>231000000003</v>
+        <v>2310000000032</v>
       </c>
       <c r="C796" s="27" t="s">
         <v>1318</v>
@@ -73902,7 +73902,7 @@
         <v>26</v>
       </c>
       <c r="B799" s="26">
-        <v>231000000004</v>
+        <v>2310000000042</v>
       </c>
       <c r="C799" s="27" t="s">
         <v>1314</v>
@@ -73938,7 +73938,7 @@
         <v>26</v>
       </c>
       <c r="B801" s="26">
-        <v>231000000005</v>
+        <v>2310000000052</v>
       </c>
       <c r="C801" s="27" t="s">
         <v>1315</v>
@@ -73990,7 +73990,7 @@
         <v>26</v>
       </c>
       <c r="B804" s="26">
-        <v>231000000007</v>
+        <v>2310000000072</v>
       </c>
       <c r="C804" s="27" t="s">
         <v>1316</v>
@@ -74333,31 +74333,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Hyperlink_test xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Hyperlink_test>
-    <file_location xmlns="3a1b5eaf-929c-4573-820b-891dab44de53" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003038969B0484BC4CA3D2193B8D466837" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a7d958e08c55628ca432b8bed74f23d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xmlns:ns3="3a1b5eaf-929c-4573-820b-891dab44de53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0851d0c4117cb1b37bf320fb4a56d55a" ns2:_="" ns3:_="">
     <xsd:import namespace="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
@@ -74613,10 +74588,46 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Hyperlink_test xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Hyperlink_test>
+    <file_location xmlns="3a1b5eaf-929c-4573-820b-891dab44de53" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCEC1A57-4DA5-4CC2-ABE5-6030A064E48B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ECD1D35-0CAC-433E-A5D6-3D3C549F3634}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
+    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -74633,20 +74644,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ECD1D35-0CAC-433E-A5D6-3D3C549F3634}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCEC1A57-4DA5-4CC2-ABE5-6030A064E48B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
-    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>